--- a/artfynd/A 29309-2022 artfynd.xlsx
+++ b/artfynd/A 29309-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,6 +2071,112 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>102849816</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599466</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7034234</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29309-2022 artfynd.xlsx
+++ b/artfynd/A 29309-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29309-2022 artfynd.xlsx
+++ b/artfynd/A 29309-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,6 +2061,702 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120536910</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599485</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7034252</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120536911</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>599324</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7034156</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120536916</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>599220</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7033975</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120536912</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>599223</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7034003</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120536909</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80499</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>599357</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7034371</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120536913</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91370</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>599346</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7034098</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29309-2022 artfynd.xlsx
+++ b/artfynd/A 29309-2022 artfynd.xlsx
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120536910</v>
+        <v>120536911</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,21 +2079,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599485</v>
+        <v>599324</v>
       </c>
       <c r="R14" t="n">
-        <v>7034252</v>
+        <v>7034156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120536911</v>
+        <v>120536912</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>91881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599324</v>
+        <v>599223</v>
       </c>
       <c r="R15" t="n">
-        <v>7034156</v>
+        <v>7034003</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120536916</v>
+        <v>120536913</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>91370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,25 +2307,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>2014</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599220</v>
+        <v>599346</v>
       </c>
       <c r="R16" t="n">
-        <v>7033975</v>
+        <v>7034098</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,22 +2369,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120536912</v>
+        <v>120536909</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>80499</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,21 +2427,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599223</v>
+        <v>599357</v>
       </c>
       <c r="R17" t="n">
-        <v>7034003</v>
+        <v>7034371</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120536909</v>
+        <v>120536910</v>
       </c>
       <c r="B18" t="n">
-        <v>80499</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599357</v>
+        <v>599485</v>
       </c>
       <c r="R18" t="n">
-        <v>7034371</v>
+        <v>7034252</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120536913</v>
+        <v>120536916</v>
       </c>
       <c r="B19" t="n">
-        <v>91370</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2014</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599346</v>
+        <v>599220</v>
       </c>
       <c r="R19" t="n">
-        <v>7034098</v>
+        <v>7033975</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,22 +2717,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 29309-2022 artfynd.xlsx
+++ b/artfynd/A 29309-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102849816</v>
+        <v>105157755</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599466</v>
+        <v>599415</v>
       </c>
       <c r="R2" t="n">
-        <v>7034233</v>
+        <v>7034188</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Maria Eriksson</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Maria Eriksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105157753</v>
+        <v>120536911</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +787,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599421.8792940762</v>
+        <v>599324</v>
       </c>
       <c r="R3" t="n">
-        <v>7034172.164791287</v>
+        <v>7034156</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,22 +845,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,31 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105157754</v>
+        <v>120536909</v>
       </c>
       <c r="B4" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,37 +898,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599412.4543596273</v>
+        <v>599357</v>
       </c>
       <c r="R4" t="n">
-        <v>7034186.659021164</v>
+        <v>7034371</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,22 +956,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,31 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105157755</v>
+        <v>110386023</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,34 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599415.5504929463</v>
+        <v>599201</v>
       </c>
       <c r="R5" t="n">
-        <v>7034188.099617789</v>
+        <v>7033981</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,37 +1080,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106564479</v>
+        <v>110386047</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,14 +1133,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärshällarna, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599472.8266872054</v>
+        <v>599172</v>
       </c>
       <c r="R6" t="n">
-        <v>7034409.443566307</v>
+        <v>7033982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,22 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,61 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106564539</v>
+        <v>110589940</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blåbärshällarna, Ång</t>
+          <t>Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599292.0236126321</v>
+        <v>599460</v>
       </c>
       <c r="R7" t="n">
-        <v>7034062.374546132</v>
+        <v>7034459</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,27 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Felicia Skorsdal</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106564524</v>
+        <v>110386012</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,42 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåbärshällarna, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599494.8761513828</v>
+        <v>599218</v>
       </c>
       <c r="R8" t="n">
-        <v>7034248.820410197</v>
+        <v>7033971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,22 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1485,15 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106552179</v>
+        <v>120536916</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,38 +1409,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599494.6810688156</v>
+        <v>599220</v>
       </c>
       <c r="R9" t="n">
-        <v>7034255.087635052</v>
+        <v>7033975</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,22 +1467,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,27 +1497,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106552188</v>
+        <v>120536913</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,38 +1520,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåbärhällorna, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599501.5884932859</v>
+        <v>599346</v>
       </c>
       <c r="R10" t="n">
-        <v>7034263.816394606</v>
+        <v>7034098</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,22 +1578,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,27 +1608,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106564533</v>
+        <v>110385919</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,42 +1631,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blåbärshällarna, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599351.3477917735</v>
+        <v>599323</v>
       </c>
       <c r="R11" t="n">
-        <v>7034044.948699054</v>
+        <v>7034163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,22 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,6 +1702,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1831,15 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110385919</v>
+        <v>105157754</v>
       </c>
       <c r="B12" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,40 +1732,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599323.0054621267</v>
+        <v>599413</v>
       </c>
       <c r="R12" t="n">
-        <v>7034162.81754333</v>
+        <v>7034187</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,22 +1786,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,34 +1800,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110385992</v>
+        <v>102849816</v>
       </c>
       <c r="B13" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,13 +1860,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599323.0054621267</v>
+        <v>599466</v>
       </c>
       <c r="R13" t="n">
-        <v>7034162.81754333</v>
+        <v>7034233</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,22 +1890,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,27 +1911,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anna-Maria Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anna-Maria Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120536910</v>
+        <v>109633233</v>
       </c>
       <c r="B14" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,41 +1934,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599485</v>
+        <v>599448</v>
       </c>
       <c r="R14" t="n">
-        <v>7034252</v>
+        <v>7034236</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2137,22 +1991,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,18 +2005,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2182,12 +2027,7 @@
         <v>120536912</v>
       </c>
       <c r="B15" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2295,57 +2135,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120536909</v>
+        <v>106552179</v>
       </c>
       <c r="B16" t="n">
-        <v>80551</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599357</v>
+        <v>599495</v>
       </c>
       <c r="R16" t="n">
-        <v>7034371</v>
+        <v>7034255</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,22 +2201,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,69 +2231,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120536911</v>
+        <v>106552188</v>
       </c>
       <c r="B17" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärhällorna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599324</v>
+        <v>599501</v>
       </c>
       <c r="R17" t="n">
-        <v>7034156</v>
+        <v>7034264</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2485,22 +2309,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,27 +2339,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120536916</v>
+        <v>106564528</v>
       </c>
       <c r="B18" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,38 +2362,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärshällarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599220</v>
+        <v>599376</v>
       </c>
       <c r="R18" t="n">
-        <v>7033975</v>
+        <v>7034071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,22 +2419,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,75 +2433,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120536913</v>
+        <v>109633193</v>
       </c>
       <c r="B19" t="n">
-        <v>91470</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2014</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599346</v>
+        <v>599529</v>
       </c>
       <c r="R19" t="n">
-        <v>7034098</v>
+        <v>7034255</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,22 +2520,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:28</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:28</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,21 +2534,1690 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110385992</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>599323</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7034163</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120536910</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>599485</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7034252</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>106564479</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blåbärshällarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>599473</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7034410</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110589934</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>599375</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7034494</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Felicia Skorsdal</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>109633218</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>599506</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7034233</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>109633294</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>599201</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7033981</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>106564524</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Blåbärshällarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>599495</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7034249</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>106564533</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blåbärshällarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>599351</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7034045</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>106564539</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blåbärshällarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>599292</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7034063</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>109633240</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>599473</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7034194</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>109633259</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>599457</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7034143</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>109633188</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>599529</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7034255</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>109633223</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>599506</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7034233</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>109633301</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>599201</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7033981</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>9 ägg i redet</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>110386039</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>599181</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7033995</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>105157753</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>599422</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7034172</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29309-2022 artfynd.xlsx
+++ b/artfynd/A 29309-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386047</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589940</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536916</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536913</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110385919</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157754</t>
         </is>
       </c>
     </row>
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102849816</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2086,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633233</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2240,6 +2315,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106552179</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106552188</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2449,6 +2534,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564528</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633193</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2651,6 +2746,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110385992</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,6 +2862,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536910</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2863,6 +2968,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564479</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2960,6 +3070,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110589934</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3065,6 +3180,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633218</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3170,6 +3290,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633294</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3275,6 +3400,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564524</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3380,6 +3510,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564533</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3485,6 +3620,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564539</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3590,6 +3730,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633240</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3695,6 +3840,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633259</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3800,6 +3950,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633188</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3905,6 +4060,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633223</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4015,6 +4175,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633301</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4117,6 +4282,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386039</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4218,8 +4388,49 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>